--- a/processed_data/hard_data_exports/hunt_tables/2026/2026_BISON_HUNTER_CHOICE.xlsx
+++ b/processed_data/hard_data_exports/hunt_tables/2026/2026_BISON_HUNTER_CHOICE.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026_bison_hunter_choice" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="2026_bison_hunter_choice" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2026_bison_hunter_choice'!$A$3:$K$17</definedName>
@@ -540,7 +540,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:K17"/>
+  <dimension ref="A1:O17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26.35" customWidth="1" min="1" max="1"/>
@@ -620,6 +620,26 @@
           <t>Notes</t>
         </is>
       </c>
+      <c r="L3" s="4" t="inlineStr">
+        <is>
+          <t>Harvest Prior Year</t>
+        </is>
+      </c>
+      <c r="M3" s="4" t="inlineStr">
+        <is>
+          <t>Harvest Success (Prior Year %)</t>
+        </is>
+      </c>
+      <c r="N3" s="4" t="inlineStr">
+        <is>
+          <t>Average Harvest Age (Prior Year)</t>
+        </is>
+      </c>
+      <c r="O3" s="4" t="inlineStr">
+        <is>
+          <t>Average Days Hunted (Prior Year)</t>
+        </is>
+      </c>
     </row>
     <row r="4" ht="24" customHeight="1">
       <c r="A4" s="5" t="inlineStr">
@@ -661,6 +681,20 @@
       <c r="I4" s="6" t="inlineStr"/>
       <c r="J4" s="6" t="inlineStr"/>
       <c r="K4" s="6" t="inlineStr"/>
+      <c r="L4" t="n">
+        <v>2025</v>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="5" ht="24" customHeight="1">
       <c r="A5" s="7" t="inlineStr">
@@ -714,6 +748,20 @@
         </is>
       </c>
       <c r="K5" s="8" t="inlineStr"/>
+      <c r="L5" t="n">
+        <v>2025</v>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="6" ht="24" customHeight="1">
       <c r="A6" s="5" t="inlineStr">
@@ -767,6 +815,20 @@
         </is>
       </c>
       <c r="K6" s="6" t="inlineStr"/>
+      <c r="L6" t="n">
+        <v>2025</v>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>93.3</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>2.4</t>
+        </is>
+      </c>
     </row>
     <row r="7" ht="24" customHeight="1">
       <c r="A7" s="7" t="inlineStr">
@@ -820,6 +882,20 @@
         </is>
       </c>
       <c r="K7" s="8" t="inlineStr"/>
+      <c r="L7" t="n">
+        <v>2025</v>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>4.5</t>
+        </is>
+      </c>
     </row>
     <row r="8" ht="24" customHeight="1">
       <c r="A8" s="5" t="inlineStr">
@@ -873,6 +949,20 @@
         </is>
       </c>
       <c r="K8" s="6" t="inlineStr"/>
+      <c r="L8" t="n">
+        <v>2025</v>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>66.7</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
     </row>
     <row r="9" ht="24" customHeight="1">
       <c r="A9" s="7" t="inlineStr">
@@ -926,6 +1016,20 @@
         </is>
       </c>
       <c r="K9" s="8" t="inlineStr"/>
+      <c r="L9" t="n">
+        <v>2025</v>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>3.5</t>
+        </is>
+      </c>
     </row>
     <row r="10" ht="24" customHeight="1">
       <c r="A10" s="5" t="inlineStr">
@@ -967,6 +1071,20 @@
       <c r="I10" s="6" t="inlineStr"/>
       <c r="J10" s="6" t="inlineStr"/>
       <c r="K10" s="6" t="inlineStr"/>
+      <c r="L10" t="n">
+        <v>2025</v>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
     </row>
     <row r="11" ht="24" customHeight="1">
       <c r="A11" s="7" t="inlineStr">
@@ -1020,6 +1138,20 @@
         </is>
       </c>
       <c r="K11" s="8" t="inlineStr"/>
+      <c r="L11" t="n">
+        <v>2025</v>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
     </row>
     <row r="12" ht="24" customHeight="1">
       <c r="A12" s="5" t="inlineStr">
@@ -1073,6 +1205,20 @@
         </is>
       </c>
       <c r="K12" s="6" t="inlineStr"/>
+      <c r="L12" t="n">
+        <v>2025</v>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>85.7</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>3.7</t>
+        </is>
+      </c>
     </row>
     <row r="13" ht="24" customHeight="1">
       <c r="A13" s="7" t="inlineStr">
@@ -1126,6 +1272,20 @@
         </is>
       </c>
       <c r="K13" s="8" t="inlineStr"/>
+      <c r="L13" t="n">
+        <v>2025</v>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
     </row>
     <row r="14" ht="24" customHeight="1">
       <c r="A14" s="5" t="inlineStr">
@@ -1179,6 +1339,20 @@
         </is>
       </c>
       <c r="K14" s="6" t="inlineStr"/>
+      <c r="L14" t="n">
+        <v>2025</v>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr"/>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>2.5</t>
+        </is>
+      </c>
     </row>
     <row r="15" ht="24" customHeight="1">
       <c r="A15" s="7" t="inlineStr">
@@ -1232,6 +1406,20 @@
         </is>
       </c>
       <c r="K15" s="8" t="inlineStr"/>
+      <c r="L15" t="n">
+        <v>2025</v>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr"/>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>4.2</t>
+        </is>
+      </c>
     </row>
     <row r="16" ht="24" customHeight="1">
       <c r="A16" s="5" t="inlineStr">
@@ -1285,6 +1473,20 @@
         </is>
       </c>
       <c r="K16" s="6" t="inlineStr"/>
+      <c r="L16" t="n">
+        <v>2025</v>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>90.9</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr"/>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>3.7</t>
+        </is>
+      </c>
     </row>
     <row r="17" ht="48" customHeight="1">
       <c r="A17" s="7" t="inlineStr">
@@ -1328,6 +1530,20 @@
       <c r="K17" s="8" t="inlineStr">
         <is>
           <t>Harvest survey due by Feb 15, 2026 | Visit: http://wildlife.utah.gov/harvest to submit your survey.</t>
+        </is>
+      </c>
+      <c r="L17" t="n">
+        <v>2024</v>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr"/>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>2</t>
         </is>
       </c>
     </row>
